--- a/AAII_Financials/Quarterly/HAS_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HAS_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="143" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="92">
   <si>
     <t>HAS</t>
   </si>
@@ -656,540 +656,553 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="40" width="13" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="41" width="13" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E7" s="2">
         <v>46110</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46019</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45928</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45837</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45746</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45655</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45564</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45200</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45109</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45018</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44920</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44829</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44738</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44647</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44556</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44465</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44374</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44283</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44192</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44101</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44010</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43919</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43828</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43737</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43464</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43282</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43191</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43009</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42918</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42827</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42729</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1139600</v>
+      </c>
+      <c r="E8" s="3">
         <v>1000200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1445900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1387500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>980800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>887100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>1101600</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>1281300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>995300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>757300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>1288900</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>1503400</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>1210000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>1001000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>1678500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>1675900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>1339200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>1163100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2013400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>1970000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>1322200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>1114800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>1723000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>1776600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>860300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>1105600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>1428000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1575200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>984500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>732500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>1389200</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>1569700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>904500</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>716300</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>1596100</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>1791500</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>972500</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>849700</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>1629900</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>1679800</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>365400</v>
+      </c>
+      <c r="E9" s="3">
         <v>317800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>580000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>536000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>316000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>268900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>463500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>484800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>328200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>263200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>856800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>669800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>606500</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>476800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>723400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>721700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>521600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>423200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>911300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>781300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>456500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>398800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>775700</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>787000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>350600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>375500</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>732600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>755100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>414800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>319900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>712300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>760900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>404400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>324800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>751500</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>869900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>447400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>306100</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>634600</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>659000</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>774200</v>
+      </c>
+      <c r="E10" s="3">
         <v>682400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>865900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>851500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>664800</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>618200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>638100</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>796500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>667100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>494100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>432100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>833600</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>603500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>524200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>955100</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>954200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>817600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>739900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>1102100</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>1188700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>865700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>716000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>947300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>989600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>509700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>730100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>695400</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>820100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>569700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>412600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>676900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>808800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>500100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>391500</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>844600</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>921600</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>525100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>543600</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>995300</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>1020800</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1232,130 +1245,134 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D12" s="3">
+        <v>93600</v>
+      </c>
+      <c r="E12" s="3">
         <v>78000</v>
       </c>
-      <c r="E12" s="3">
+      <c r="F12" s="3">
         <v>130000</v>
       </c>
-      <c r="F12" s="3">
+      <c r="G12" s="3">
         <v>97600</v>
       </c>
-      <c r="G12" s="3">
+      <c r="H12" s="3">
         <v>77500</v>
       </c>
-      <c r="H12" s="3">
+      <c r="I12" s="3">
         <v>80500</v>
       </c>
-      <c r="I12" s="3">
+      <c r="J12" s="3">
         <v>81900</v>
       </c>
-      <c r="J12" s="3">
+      <c r="K12" s="3">
         <v>76300</v>
       </c>
-      <c r="K12" s="3">
+      <c r="L12" s="3">
         <v>70400</v>
       </c>
-      <c r="L12" s="3">
+      <c r="M12" s="3">
         <v>65500</v>
       </c>
-      <c r="M12" s="3">
+      <c r="N12" s="3">
         <v>74500</v>
       </c>
-      <c r="N12" s="3">
+      <c r="O12" s="3">
         <v>76700</v>
       </c>
-      <c r="O12" s="3">
+      <c r="P12" s="3">
         <v>72400</v>
       </c>
-      <c r="P12" s="3">
+      <c r="Q12" s="3">
         <v>83300</v>
       </c>
-      <c r="Q12" s="3">
+      <c r="R12" s="3">
         <v>76700</v>
       </c>
-      <c r="R12" s="3">
+      <c r="S12" s="3">
         <v>82400</v>
       </c>
-      <c r="S12" s="3">
+      <c r="T12" s="3">
         <v>79200</v>
       </c>
-      <c r="T12" s="3">
+      <c r="U12" s="3">
         <v>69600</v>
       </c>
-      <c r="U12" s="3">
+      <c r="V12" s="3">
         <v>86600</v>
       </c>
-      <c r="V12" s="3">
+      <c r="W12" s="3">
         <v>80100</v>
       </c>
-      <c r="W12" s="3">
+      <c r="X12" s="3">
         <v>87200</v>
       </c>
-      <c r="X12" s="3">
+      <c r="Y12" s="3">
         <v>61800</v>
       </c>
-      <c r="Y12" s="3">
+      <c r="Z12" s="3">
         <v>84700</v>
       </c>
-      <c r="Z12" s="3">
+      <c r="AA12" s="3">
         <v>62700</v>
       </c>
-      <c r="AA12" s="3">
+      <c r="AB12" s="3">
         <v>58300</v>
       </c>
-      <c r="AB12" s="3">
+      <c r="AC12" s="3">
         <v>53800</v>
       </c>
-      <c r="AC12" s="3">
+      <c r="AD12" s="3">
         <v>72900</v>
       </c>
-      <c r="AD12" s="3">
+      <c r="AE12" s="3">
         <v>67400</v>
       </c>
-      <c r="AE12" s="3">
+      <c r="AF12" s="3">
         <v>65600</v>
       </c>
-      <c r="AF12" s="3">
+      <c r="AG12" s="3">
         <v>56300</v>
       </c>
-      <c r="AG12" s="3">
+      <c r="AH12" s="3">
         <v>63100</v>
       </c>
-      <c r="AH12" s="3">
+      <c r="AI12" s="3">
         <v>65800</v>
       </c>
-      <c r="AI12" s="3">
+      <c r="AJ12" s="3">
         <v>59900</v>
       </c>
-      <c r="AJ12" s="3">
+      <c r="AK12" s="3">
         <v>57400</v>
       </c>
-      <c r="AK12" s="3">
+      <c r="AL12" s="3">
         <v>76300</v>
       </c>
-      <c r="AL12" s="3">
+      <c r="AM12" s="3">
         <v>67400</v>
       </c>
-      <c r="AM12" s="3">
+      <c r="AN12" s="3">
         <v>62800</v>
       </c>
-      <c r="AN12" s="3">
+      <c r="AO12" s="3">
         <v>62600</v>
       </c>
-      <c r="AO12" s="3">
+      <c r="AP12" s="3">
         <v>75500</v>
       </c>
-      <c r="AP12" s="3">
+      <c r="AQ12" s="3">
         <v>70100</v>
       </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>8</v>
       </c>
@@ -1476,97 +1493,100 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D14" s="3">
+        <v>-200</v>
+      </c>
+      <c r="E14" s="3">
         <v>4100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>2100</v>
       </c>
-      <c r="F14" s="3" t="s">
+      <c r="G14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="G14" s="3">
-        <v>1021900</v>
-      </c>
       <c r="H14" s="3">
+        <v>1021700</v>
+      </c>
+      <c r="I14" s="3">
         <v>25600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>128200</v>
       </c>
-      <c r="J14" s="3" t="s">
+      <c r="K14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>19700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>14800</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1059100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>481400</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>306600</v>
       </c>
-      <c r="P14" s="3" t="s">
+      <c r="Q14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>379200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>58600</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>3200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>2300</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>8900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>2000</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>113200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>1900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>52600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>5900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>10300</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>149800</v>
       </c>
-      <c r="AC14" s="3" t="s">
+      <c r="AD14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
       <c r="AE14" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="3">
         <v>110800</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>24</v>
@@ -1580,8 +1600,8 @@
       <c r="AJ14" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AK14" s="3">
-        <v>0</v>
+      <c r="AK14" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AL14" s="3">
         <v>0</v>
@@ -1598,8 +1618,11 @@
       <c r="AP14" s="3">
         <v>0</v>
       </c>
+      <c r="AQ14" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>10</v>
       </c>
@@ -1610,16 +1633,16 @@
         <v>14600</v>
       </c>
       <c r="F15" s="3">
-        <v>17200</v>
+        <v>14600</v>
       </c>
       <c r="G15" s="3">
         <v>17200</v>
       </c>
       <c r="H15" s="3">
+        <v>17200</v>
+      </c>
+      <c r="I15" s="3">
         <v>17000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>17100</v>
       </c>
       <c r="J15" s="3">
         <v>17100</v>
@@ -1628,58 +1651,58 @@
         <v>17100</v>
       </c>
       <c r="L15" s="3">
+        <v>17100</v>
+      </c>
+      <c r="M15" s="3">
         <v>17000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>17900</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>19200</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>22800</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>23100</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>24100</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>26900</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>27200</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>27100</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>26500</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>27700</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>29700</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>32900</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>37100</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>36200</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>34700</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>36800</v>
-      </c>
-      <c r="AC15" s="3">
-        <v>11800</v>
       </c>
       <c r="AD15" s="3">
         <v>11800</v>
@@ -1691,37 +1714,40 @@
         <v>11800</v>
       </c>
       <c r="AG15" s="3">
-        <v>8800</v>
+        <v>11800</v>
       </c>
       <c r="AH15" s="3">
         <v>8800</v>
       </c>
       <c r="AI15" s="3">
+        <v>8800</v>
+      </c>
+      <c r="AJ15" s="3">
         <v>4600</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>6500</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>6600</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>6500</v>
-      </c>
-      <c r="AM15" s="3">
-        <v>7900</v>
       </c>
       <c r="AN15" s="3">
         <v>7900</v>
       </c>
       <c r="AO15" s="3">
-        <v>8700</v>
+        <v>7900</v>
       </c>
       <c r="AP15" s="3">
         <v>8700</v>
       </c>
+      <c r="AQ15" s="3">
+        <v>8700</v>
+      </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1761,252 +1787,259 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="3">
+        <v>887100</v>
+      </c>
+      <c r="E17" s="3">
         <v>724300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>1147000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>1046400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>757100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>689600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>992100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>979400</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>763500</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>626300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>1428400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>1191500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>1092000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>983100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>1804200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>1481600</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>1120100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>1043100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>1841900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>1602100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>1245600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>967500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>1536600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>1440100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>858100</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>1128900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>1237600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1278000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>967000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>696400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1378600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1256400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>816900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>796800</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1325000</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1430600</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>872500</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>771300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1374800</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>1317700</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D18" s="3">
+        <v>252500</v>
+      </c>
+      <c r="E18" s="3">
         <v>275900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>298900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>341100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>223700</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>197500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>109500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>301900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>231800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>131000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-139500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>311900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>118000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>17900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-125700</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>194300</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>219100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>120000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>171500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>367900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>76600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>147300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>186400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>336500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>2200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-23300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>190400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>297200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>17500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>36100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>10600</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>313400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>87600</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>-80500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>271100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>360900</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>100000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>78400</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>255100</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>362100</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>13</v>
       </c>
@@ -2049,347 +2082,354 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>14</v>
       </c>
       <c r="D20" s="3">
+        <v>10400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-4000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-6500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1400</v>
       </c>
-      <c r="G20" s="3">
-        <v>-18700</v>
-      </c>
       <c r="H20" s="3">
+        <v>-18500</v>
+      </c>
+      <c r="I20" s="3">
         <v>2600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>6300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-19900</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>5000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>7700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>7300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>13200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>1800</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-41200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>10600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>30100</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>12100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>6100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>143200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-14700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>10600</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>15800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>6700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>5200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>14900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>32000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>14000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>11100</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>16900</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-10000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>8500</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D21" s="3">
+        <v>256700</v>
+      </c>
+      <c r="E21" s="3">
         <v>294500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>320000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>356900</v>
       </c>
-      <c r="G21" s="3">
-        <v>259600</v>
-      </c>
       <c r="H21" s="3">
+        <v>259400</v>
+      </c>
+      <c r="I21" s="3">
         <v>211900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>120300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>338900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>249700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>143000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-129300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>328900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>142300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>42400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-61400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>267100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>285400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>174000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>203900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>443000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>159500</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>235300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>249100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>422300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>73500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>43300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>377900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>332900</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>75300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>90800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>60500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>370000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>131600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>-32900</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>344800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>423500</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>157100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>130900</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>284100</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>411600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D22" s="3">
+        <v>46500</v>
+      </c>
+      <c r="E22" s="3">
         <v>41800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>40400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>40800</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>40600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>41600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>43500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>46200</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>43000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>38500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>46300</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>47100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>46600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>46300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>45800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>41900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>41700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>41600</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>42400</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>43300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>46100</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>47900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>47400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>49400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>49600</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>54700</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>34800</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>22800</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>22000</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>22300</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>22400</v>
-      </c>
-      <c r="AH22" s="3">
-        <v>22800</v>
       </c>
       <c r="AI22" s="3">
         <v>22800</v>
@@ -2398,269 +2438,278 @@
         <v>22800</v>
       </c>
       <c r="AK22" s="3">
+        <v>22800</v>
+      </c>
+      <c r="AL22" s="3">
         <v>24500</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>25100</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>24200</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>24500</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>25100</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>24300</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D23" s="3">
+        <v>208700</v>
+      </c>
+      <c r="E23" s="3">
         <v>244100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>270900</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>305200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-814700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>136600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-57200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>290300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>182900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>81000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-1245200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-215000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>-227900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-21000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-164200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>165600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>179900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>80200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>87900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>323400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>41100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>129500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>138500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>299200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-43700</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-71900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>298800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>259700</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>6100</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>29600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>-5100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>295800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>68100</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>-88400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>278600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>349800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>86900</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>70800</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>219900</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>346300</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D24" s="3">
+        <v>47400</v>
+      </c>
+      <c r="E24" s="3">
         <v>44600</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>67800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>71300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>40000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>37100</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>-30700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>67000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>44400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>21900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-184400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>-44600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>7000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-35600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>37400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>39400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>17300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3100</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>68500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>23600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>12000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>32300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>79200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-10800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-4100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>31400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>46800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-7300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2900</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-24000</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>49200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>7800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-23700</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>-32500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>84300</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>19200</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>2200</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>39300</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>90200</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>19</v>
       </c>
@@ -2781,252 +2830,261 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>20</v>
       </c>
       <c r="D26" s="3">
+        <v>161300</v>
+      </c>
+      <c r="E26" s="3">
         <v>199500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>203100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>233900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>-854700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>99500</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-26500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>223300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>138500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>59100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-1060800</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-170400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>-234900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-21700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-128600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>128200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>140500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>62900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>84800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>254900</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>17500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>117500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>106200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>220000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-32900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-67800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>267300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>212900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>13400</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>26700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>18900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>246600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>60300</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>-64700</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>311100</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>265600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>67700</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>68600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>180600</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>256200</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3">
+        <v>160900</v>
+      </c>
+      <c r="E27" s="3">
         <v>198400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>201600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>233200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>-855800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>98600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-34300</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>223200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>138500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>58200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-1061100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-171100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>-235000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-22100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-128900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>129200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>142000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>61200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>82200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>253200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>16500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>116200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>105200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>220900</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-33900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-69600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>267300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>212900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>13400</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>26700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>18900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>246600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>60300</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-64700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>311100</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>265600</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>67700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>68600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>192700</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>257800</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>22</v>
       </c>
@@ -3147,8 +3205,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>23</v>
       </c>
@@ -3191,8 +3252,8 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>24</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>24</v>
@@ -3203,17 +3264,17 @@
       <c r="T29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
+      <c r="U29" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="V29" s="3">
         <v>0</v>
       </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>-39400</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>24</v>
@@ -3227,11 +3288,11 @@
       <c r="AB29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AC29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AD29" s="3" t="s">
+      <c r="AC29" s="3" t="s">
         <v>24</v>
+      </c>
+      <c r="AD29" s="3">
+        <v>0</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>24</v>
@@ -3239,23 +3300,23 @@
       <c r="AF29" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-10200</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>17300</v>
       </c>
-      <c r="AI29" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-47800</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>-316400</v>
-      </c>
-      <c r="AL29" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AM29" s="3" t="s">
         <v>24</v>
@@ -3269,8 +3330,11 @@
       <c r="AP29" s="3" t="s">
         <v>24</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>24</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3391,8 +3455,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3513,252 +3580,261 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-10400</v>
+      </c>
+      <c r="E32" s="3">
         <v>4000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>6500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1400</v>
       </c>
-      <c r="G32" s="3">
-        <v>18700</v>
-      </c>
       <c r="H32" s="3">
+        <v>18500</v>
+      </c>
+      <c r="I32" s="3">
         <v>-2600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-6300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>19900</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-5000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-7700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-7300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-13200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-1800</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>41200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-10600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-30100</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-12100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-6100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-143200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>14700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-10600</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-15800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-6700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-5200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-3300</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-14900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-32000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-14000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-11100</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-16900</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>10000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-8500</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>160900</v>
+      </c>
+      <c r="E33" s="3">
         <v>198400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>201600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>233200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>-855800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>98600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-34300</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>223200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>138500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>58200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-1061100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-171100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>-235000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-22100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-128900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>129200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>142000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>61200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>82200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>253200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-22900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>116200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>105200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>220900</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-33900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-69600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>267300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>212900</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>13400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>26700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>8800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>263900</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>60300</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>-112500</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-5300</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>265600</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>67700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>68600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>192700</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>257800</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3879,257 +3955,266 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>160900</v>
+      </c>
+      <c r="E35" s="3">
         <v>198400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>201600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>233200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>-855800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>98600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-34300</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>223200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>138500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>58200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-1061100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-171100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>-235000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-22100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-128900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>129200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>142000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>61200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>82200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>253200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-22900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>116200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>105200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>220900</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-33900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-69600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>267300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>212900</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>13400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>26700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>8800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>263900</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>60300</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>-112500</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-5300</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>265600</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>67700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>68600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>192700</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>257800</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E38" s="2">
         <v>46110</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46019</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45928</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45837</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45746</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45655</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45564</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45200</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45109</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45018</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44920</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44829</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44738</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44647</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44556</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44465</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44374</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44283</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44192</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44101</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44010</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43919</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43828</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43737</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43464</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43282</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43191</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43009</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42918</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42827</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42729</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4172,8 +4257,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4216,142 +4302,146 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>880500</v>
+      </c>
+      <c r="E41" s="3">
         <v>857100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>776200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>620600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>546600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>620800</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>694700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>695800</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>626500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>569300</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>544800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>184400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>211700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>372800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>498600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>545500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>628200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1057900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1019200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>1181200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>1228200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>1430400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1449700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1132400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1038000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1237900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4580400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>1060400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>1151000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>1196600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>1182400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>907100</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>1159100</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>1598900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>1581200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>1244800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>1433500</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>1463100</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>1282300</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>830400</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>497700</v>
+      </c>
+      <c r="E42" s="3">
         <v>498200</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>105400</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -4362,14 +4452,14 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>489300</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>483000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
         <v>0</v>
       </c>
@@ -4382,12 +4472,12 @@
       <c r="P42" s="3">
         <v>0</v>
       </c>
-      <c r="Q42" s="3" t="s">
+      <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
       <c r="S42" s="3">
         <v>0</v>
       </c>
@@ -4460,496 +4550,511 @@
       <c r="AP42" s="3">
         <v>0</v>
       </c>
+      <c r="AQ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>843700</v>
+      </c>
+      <c r="E43" s="3">
         <v>841000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1360400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1125000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>847000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>771800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1220400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1242800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>948300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>632500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1114900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1102000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>877000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>685200</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1132400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1550000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1290200</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1231500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1787300</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1739900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1123800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>810400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1615600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1710100</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1164200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1234900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1410600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1416900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>805300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>638400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1188100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1391200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>739300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>612700</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1405400</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1655800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>846500</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>676900</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1320000</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>1452900</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>353200</v>
+      </c>
+      <c r="E44" s="3">
         <v>280500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>259800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>396700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>417100</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>295800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>274200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>375400</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>357600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>336200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>332000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>617700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>731300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>713400</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>676800</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>844500</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>867500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>644300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>552100</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>544100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>499600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>429200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>395600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>540000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>564200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>444400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>446100</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>589100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>564800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>491800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>443400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>610900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>610200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>517400</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>433300</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>629100</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>557500</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>416200</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>387700</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>607700</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E45" s="3">
         <v>1500</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>1100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>900</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>4900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>9700</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1700</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>8400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>1062400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>691300</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>320500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>299500</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>321600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>369500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>265200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>764800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>566000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>385700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>376400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>419300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>401300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>310500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>346700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>309000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>305100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>268700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>283200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>319000</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>292800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>214000</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>232600</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>257300</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>243500</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>237700</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>256000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>2849600</v>
+      </c>
+      <c r="E46" s="3">
         <v>2765000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>2583700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>2410000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>2041200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>1912800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>2242500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>3021600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>2674400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>1995400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>2323600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>3240100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>2509000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>2539200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>2999100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>3260500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>3085400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>3255300</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>3728100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>3730400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>3616400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>3236000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>3846600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>3759000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>3185700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3318500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>6747500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3413100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>2830100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>2631900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3082500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3192500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>2827600</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3021800</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3633900</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>3762200</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>3094800</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>2799700</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>3227600</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>3147000</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4995,41 +5100,41 @@
       <c r="Q47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="R47" s="3">
+      <c r="R47" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="S47" s="3">
         <v>157500</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>148200</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>94600</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>104200</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>108100</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>72600</v>
       </c>
-      <c r="X47" s="3" t="s">
+      <c r="Y47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>43700</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>84900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>108500</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>87500</v>
-      </c>
-      <c r="AC47" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="AD47" s="3" t="s">
         <v>24</v>
@@ -5046,8 +5151,8 @@
       <c r="AH47" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="AI47" s="3">
-        <v>0</v>
+      <c r="AI47" s="3" t="s">
+        <v>24</v>
       </c>
       <c r="AJ47" s="3">
         <v>0</v>
@@ -5070,252 +5175,261 @@
       <c r="AP47" s="3">
         <v>0</v>
       </c>
+      <c r="AQ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>453900</v>
+      </c>
+      <c r="E48" s="3">
         <v>393900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>247800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>243000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>251800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>293600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>302600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>564200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>542900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>501300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>334300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>474600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>515400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>509100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>422800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>411800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>409900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>422600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>421100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>441900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>466200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>482700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>489000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>477200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>482200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>455900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>382200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>371900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>387400</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>395600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>256500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>255200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>265900</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>262400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>259700</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>263900</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>269000</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>270000</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>267400</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>247200</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2168500</v>
+      </c>
+      <c r="E49" s="3">
         <v>2214600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2196700</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2197800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2186900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>3192100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3185800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2963500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2976300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3013800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3051300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3893900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4913100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>5216500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4284700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>4549500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>4640100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>4555900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>4591600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>4629700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>4669100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5204400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>5222500</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>5190900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5225100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5188400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1140900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1143400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1156000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1167600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>1179700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>1304600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>1313600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>784500</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>790400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>796500</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>802300</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>809000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>816500</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>859300</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5436,8 +5550,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5558,130 +5675,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>136300</v>
+      </c>
+      <c r="E52" s="3">
         <v>125300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>96500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>294500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>109900</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>112400</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>122900</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>273500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>273100</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>692500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>403800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>731600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>672200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>658900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>1589300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>1246800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>1219400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>1190300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>1192800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>1320300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>1277900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>1266000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>1216500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>1191200</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>1220500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>1374000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>585000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>626200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>665200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>739700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>744300</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>743100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>706800</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>660300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>605900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>722100</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>746600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>767100</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>779900</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>701600</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5802,130 +5925,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6037200</v>
+      </c>
+      <c r="E54" s="3">
         <v>5930300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>5552000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>5521800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>5174400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6040000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6340300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>7229900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6864100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>6203000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6540900</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>8340200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>8609700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>8923700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>9295900</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>9626100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>9503000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>9518700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>10037800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>10230400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>10102200</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>10189100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>10818400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>10703200</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>10222100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>10424400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>8855600</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>5554600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>5038600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>4934800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>5263000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>5495300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>5113900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>4729100</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>5290000</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>5544600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>4912700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>4645900</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>5091400</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>4955100</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5968,8 +6097,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6012,740 +6142,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>374900</v>
+      </c>
+      <c r="E57" s="3">
         <v>280700</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>335400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>381400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>339600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>284800</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>341500</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>420300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>297500</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>254200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>340600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>372300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>363400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>360100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>427300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>559500</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>543800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>411700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>580200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>598200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>382400</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>312100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>425500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>466200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>335200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>308500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>343900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>501100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>330100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>234300</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>333500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>458800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>339900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>256400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>348500</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>525900</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>368300</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>241200</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>319500</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>344900</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>527800</v>
+      </c>
+      <c r="E58" s="3">
         <v>528400</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>527600</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>27500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>27900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>28800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>29800</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>532200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>532700</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>529100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>530500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>88100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>252800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>281400</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>255600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>244900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>235000</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>259900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>200900</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>188500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>190400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>157700</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>439200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>379300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>385000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>73800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>7900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>12800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>13400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>9700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>20300</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>20100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>21600</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>155000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>189000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>536800</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>415100</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>522300</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>528300</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>205200</v>
+      </c>
+      <c r="E59" s="3">
         <v>248700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>239000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>265000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>250200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>314200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>387200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>220800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>218000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>296500</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>294400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>876400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>558800</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>525000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1506800</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1552500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1379400</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1371400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1674800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1663700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1472800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1283600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1538600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1470100</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1261400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1356200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>912700</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>957700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>729900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>701100</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>931100</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>842800</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>692500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>574500</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>748300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>769900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>567200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>545500</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>776000</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>742600</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1715300</v>
+      </c>
+      <c r="E60" s="3">
         <v>1671400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1871100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1413600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1227800</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1156000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>1401300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2052800</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1830100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1792200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2056400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2024200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1950400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>1897400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2189700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2356900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2158200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2043000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2455900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2450400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2045600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1753400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2403300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2315500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1981600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1738600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1257100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1466700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1072700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>948700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>1274300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>1321900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>1052400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>852500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>1251700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>1484800</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>1472200</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>1201800</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>1617900</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>1615700</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>3350400</v>
+      </c>
+      <c r="E61" s="3">
         <v>3344800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2868700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>3318800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>3320900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>3331500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>3380800</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>3462600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>3461400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2966900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2965800</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>3773000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>3814300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>3831700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>3711200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>3725100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>3739000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>3737900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>3824200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>3977400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>4388700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4674100</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>4660000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>4777800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4802500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>5156300</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4046500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1696200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1695800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1695500</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1695100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1694700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1694400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1694000</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1693600</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1693300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1199100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1198900</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>1198700</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>1198500</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>241000</v>
+      </c>
+      <c r="E62" s="3">
         <v>239900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>144400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>355600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>356000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>355000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>263300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>404800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>224000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>414000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>181100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>319800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>374800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>435900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>533100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>545100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>570000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>633600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>670700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>722500</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>753000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>777700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>793900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>778500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>771700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>739000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>556600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>550800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>554200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>636100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>539100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>591400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>600300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>611200</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>514700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>410400</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>408900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>393500</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>389400</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>364400</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6866,8 +7015,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>19</v>
       </c>
@@ -6988,8 +7140,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7110,130 +7265,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5306900</v>
+      </c>
+      <c r="E66" s="3">
         <v>5256100</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>4986500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5088000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>4904700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>4842500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5155300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5920200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5691200</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5173100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5453900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6117000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6139500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6165000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6463100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6650100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6519400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>6472700</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7011900</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7211400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7251700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7269600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>7921700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>7929400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>7618000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>7695100</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5860100</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>3713700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>3322700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>3280200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>3508500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>3608000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>3347100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>3157700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>3460000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>3588400</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>3080200</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>2794200</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>3228600</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>3213400</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7276,8 +7437,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7398,8 +7560,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7520,8 +7685,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7642,8 +7810,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7764,130 +7935,136 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>1712900</v>
+      </c>
+      <c r="E72" s="3">
         <v>1652500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>1554100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>1452400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>1319300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2274400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2274200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2408200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2284700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2148000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2188400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>3348300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>3618100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>3951800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>4071400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>4297800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>4265900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>4220900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>4257800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>4269600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>4110300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>4226800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>4204200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>4192400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>4064700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>4191800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>4354600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>4180300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>4053300</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4125700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4184400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4254900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4070700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4090600</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4260200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4336400</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>4141900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>4145500</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>4148700</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>4019400</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -8008,8 +8185,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8130,8 +8310,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8252,130 +8435,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>705200</v>
+      </c>
+      <c r="E76" s="3">
         <v>648300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>538500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>406400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>241100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>1169900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>1157600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>1287200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>1150600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>1005900</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>1061900</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>2197800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>2443000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>2730800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>2832800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>2976000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>2983600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>3046000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>3025900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>3019000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>2850500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>2919500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>2896700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>2773800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>2604000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>2729200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>2995500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>1840900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>1715900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>1654500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>1754500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>1887300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>1766800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>1571400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>1830000</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>1956300</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>1832500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>1851600</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>1862700</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>1741800</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8496,257 +8685,266 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46201</v>
+      </c>
+      <c r="E80" s="2">
         <v>46110</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46019</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45928</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45837</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45746</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45655</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45564</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45200</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45109</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45018</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44920</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44829</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44738</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44647</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44556</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44465</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44374</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44283</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44192</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44101</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44010</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43919</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43828</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43737</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43464</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43282</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43191</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43009</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42918</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42827</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42729</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42638</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>160900</v>
+      </c>
+      <c r="E81" s="3">
         <v>198400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>201600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>233200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>-855800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>98600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-34300</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>223200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>138500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>58200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-1061100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-171100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>-235000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-22100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-128900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>129200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>142000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>61200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>82200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>253200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-22900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>116200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>105200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>220900</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-33900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-69600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>267300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>212900</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>13400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>26700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>8800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>263900</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>60300</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>-112500</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-5300</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>265600</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>67700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>68600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>192700</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>257800</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8789,130 +8987,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E83" s="3">
         <v>17200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>20700</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>24400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>28300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>21300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>39700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>33400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>30700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>23900</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>32900</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>32700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>36600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>25100</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>57000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>59600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>63800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>52200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>73600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>76300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>72300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>57900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>63200</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>73700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>67600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>60500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>44300</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>50400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>47200</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>38800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>43200</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>51500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>40600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>32700</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>41700</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>48600</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>46000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>35600</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>39100</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>40900</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9033,8 +9235,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9155,8 +9360,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9277,8 +9485,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9399,8 +9610,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9521,130 +9735,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>266700</v>
+      </c>
+      <c r="E89" s="3">
         <v>337700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>403200</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>280600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>71300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>138100</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>259800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>222500</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>187300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>177800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>390700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>215700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>30400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>88800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>115500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>109600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>13100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>134700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>132300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>126700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>181300</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>377600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>482000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>236000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>-33300</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>291600</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>263500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>53300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>71800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>264500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>471300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-66100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-76900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>317700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>522600</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-164300</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>-45800</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>411900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>621900</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>-73400</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9687,130 +9907,134 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-22200</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-19700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-16100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-13800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-19300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-18400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-27400</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-22100</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>24900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-48300</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-58900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-53200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-43500</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-54900</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-46600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-29200</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-34600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-35000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-39200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-23900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-33700</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-28100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-33200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-30800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-42800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-32600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-33000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-25200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-36400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-32300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-43500</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-28200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-32400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-36200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-36100</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-30200</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-102500</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-140900</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9931,8 +10155,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10053,130 +10280,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-52500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-472100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-92600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-102600</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-36800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-52400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>431700</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-60000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-527300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-48100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>280200</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-46800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-60200</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-55600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-47200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-53200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-188700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-23900</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-35500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>343800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-40800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-25500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-28500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-16900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-24300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4430500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>25500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-26000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-33500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-27000</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-35600</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-27100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-197600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-26200</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-34500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-29200</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-36800</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-31000</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-47900</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-44500</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10219,40 +10452,41 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>99100</v>
+      </c>
+      <c r="E96" s="3">
         <v>98500</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>98300</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>98200</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>98100</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>97900</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>97700</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>97600</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>97400</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>97200</v>
-      </c>
-      <c r="M96" s="3">
-        <v>97100</v>
       </c>
       <c r="N96" s="3">
         <v>97100</v>
@@ -10261,88 +10495,91 @@
         <v>97100</v>
       </c>
       <c r="P96" s="3">
+        <v>97100</v>
+      </c>
+      <c r="Q96" s="3">
         <v>96700</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-96700</v>
       </c>
       <c r="R96" s="3">
         <v>-96700</v>
       </c>
       <c r="S96" s="3">
+        <v>-96700</v>
+      </c>
+      <c r="T96" s="3">
         <v>-97400</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-94500</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-93800</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-93200</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-94100</v>
       </c>
-      <c r="X96" s="3">
+      <c r="Y96" s="3">
         <v>-93400</v>
-      </c>
-      <c r="Y96" s="3">
-        <v>-93200</v>
       </c>
       <c r="Z96" s="3">
         <v>-93200</v>
       </c>
       <c r="AA96" s="3">
+        <v>-93200</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-93100</v>
       </c>
-      <c r="AB96" s="3">
+      <c r="AC96" s="3">
         <v>-93200</v>
       </c>
-      <c r="AC96" s="3">
+      <c r="AD96" s="3">
         <v>-85800</v>
       </c>
-      <c r="AD96" s="3">
+      <c r="AE96" s="3">
         <v>-85900</v>
       </c>
-      <c r="AE96" s="3">
+      <c r="AF96" s="3">
         <v>-85600</v>
       </c>
-      <c r="AF96" s="3">
+      <c r="AG96" s="3">
         <v>-79300</v>
       </c>
-      <c r="AG96" s="3">
+      <c r="AH96" s="3">
         <v>-79700</v>
       </c>
-      <c r="AH96" s="3">
+      <c r="AI96" s="3">
         <v>-80000</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>-78700</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>-70800</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>-71000</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>-71400</v>
       </c>
-      <c r="AM96" s="3">
+      <c r="AN96" s="3">
         <v>-71300</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>-63400</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>-63600</v>
       </c>
-      <c r="AP96" s="3">
+      <c r="AQ96" s="3">
         <v>-64000</v>
       </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10463,8 +10700,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10585,8 +10825,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10707,370 +10950,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-191600</v>
+      </c>
+      <c r="E100" s="3">
         <v>215100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-156200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-100500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-112200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-162400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-688300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-97700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>397400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-108900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-400100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-121800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-139600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-156600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-110300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-123100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-242400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-77500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-236300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-505100</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-347600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-370800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-144600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-127900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-141000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>819500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>3227800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-110600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-86200</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-220400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-158600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-157300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-145500</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-275700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-150900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-800</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>51200</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-211700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-115700</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>64800</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>3500</v>
+      </c>
+      <c r="E101" s="3">
         <v>2800</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-4300</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>4500</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>18700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-7800</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-200</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-9900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-11700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>5400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-9900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-11700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>5400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-22500</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-12400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>4900</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>8400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>3300</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1300</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-23100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>3200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-7300</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>2300</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-1500</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>-19800</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>1900</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>5600</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>1800</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>11600</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-5600</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>23400</v>
+      </c>
+      <c r="E102" s="3">
         <v>80500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>155700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>74000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-74200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-73900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>69300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>56600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>24800</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>289500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>39300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-169600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-126900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-38500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-76600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-429700</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>38700</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-162000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-47000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-202200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-19300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>317300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>94400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-199900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-3342500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>3519900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-90600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-45600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>14300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>275300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-252000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-439900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>17700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>336500</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-188700</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-29600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>180800</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>451900</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>-93700</v>
       </c>
     </row>
